--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -620,34 +620,33 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Accent Set</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ARTH 2Pc Accent Set (Chair  and  Side Table)</t>
+          <t>ARTH 2Pc Accent Set (Chair and Side Table)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ARTH 2Pc Accent Set (Chair  and  Side Table) shapes a comfortable living space with an easy, coordinated presence. This living accent set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.
-Product Dimensions: TABLE: 22.8" L x 29.1" W x 29.1" H, CHAIR: 23.6" L x 23.6" W x 19.7" H
+ARTH 2Pc Accent Set (Chair and Side Table) shapes a comfortable living space with an easy, coordinated presence. This living accent set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.
+Product Dimensions: TABLE: 22.8"L X 29.1"W X 29.1"H, CHAIR: 23.6"L X 23.6"W X 19.7"H
 Features
-- Wingback Chair
-Included items and dimensions:
+- Wingback Chair Included items and dimensions:
 - Side Table: color: Walnut; dimensions: 23.5" W x 23.5"D x 19.5" H; feature: Mid-Century Modern
-- Accent Chair: color: Walnut  or  Beige; dimensions: 23" W x 29"D x 29" H; feature: Mid-Century Modern
-Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer
+- Accent Chair: color: Walnut or Beige; dimensions: 23" W x 29"D x 29" H; feature: Mid-Century Modern
+Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.
 Color: Walnut
 Weight: 39.6 lbs</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ARTH 2Pc Accent Set (Chair  and  Side Table) in Walnut | GOODDEGG</t>
+          <t>ARTH 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -737,34 +736,33 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Accent Set</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SPIEZ 2Pc Accent Set (Chair  and  Side Table)</t>
+          <t>SPIEZ 2Pc Accent Set (Chair and Side Table)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SPIEZ 2Pc Accent Set (Chair  and  Side Table) ties the living space together with a balanced, inviting feel. As a living accent set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Walnut tones, the Fabric, Solid Wood, Engineered Wood, Wood Veneer build keeps the look polished and practical.
-Product Dimensions: TABLE: 19.7" L x 19.7" W x 19.7" H, CHAIR: 24.4" L x 26.8" W x 28.3" H
+SPIEZ 2Pc Accent Set (Chair and Side Table) ties the living space together with a balanced, inviting feel. As a living accent set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Walnut tones, the Fabric, Solid Wood, Engineered Wood, Wood Veneer build keeps the look polished and practical.
+Product Dimensions: TABLE: 19.7"L X 19.7"W X 19.7"H, CHAIR: 24.4"L X 26.8"W X 28.3"H
 Features
-- Wingback Chair
-Included items and dimensions:
+- Wingback Chair Included items and dimensions:
 - Side Table: color: Walnut; dimensions: 19.5" W x 19.5"D x 19.5" H; feature: Mid-Century Modern
-- Accent Chair: color: Walnut  or  Beige; dimensions: 24.5" W x 27"D x 28" H; feature: Mid-Century Modern
-Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer
+- Accent Chair: color: Walnut or Beige; dimensions: 24.5" W x 27"D x 28" H; feature: Mid-Century Modern
+Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.
 Color: Walnut
 Weight: 33 lbs</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SPIEZ 2Pc Accent Set (Chair  and  Side Table) in Walnut | GOODDEGG</t>
+          <t>SPIEZ 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,7 +852,7 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
@@ -867,20 +865,19 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-BROMOAK Entertainment Center ties the living space together with a balanced, inviting feel. As a living tv console, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, Others, then finished in Weathered Oak tones to suit a range of interiors.
-Product Dimensions: 130" W x 23.5"D x 90" H
+BROMOAK Entertainment Center ties the living space together with a balanced, inviting feel. As a living tv console, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Weathered Oak tones to suit a range of interiors.
+Product Dimensions: 130"W X 23.5"D X 90"H
 Features
 - Traditional
 - Dentil Moldings
 - Reeded Posts
-- Carved Details
-Included items and dimensions:
+- Carved Details Included items and dimensions:
 - Left Facing Unit Base: color: Weathered Oak; dimensions: 27.75" L x 21.75" W x 34" H; feature: Traditional
 - Left Facing Unit Top: color: Weathered Oak; dimensions: 32" L x 23" W x 56" H; feature: Traditional
 - Right Facing Unit Base: color: Weathered Oak; dimensions: 27.75" L x 21.75" W x 34" H; feature: Traditional
 - Right Facing Unit Top: color: Weathered Oak; dimensions: 32" L x 23" W x 56" H; feature: Traditional
 - Console Base: color: Weathered Oak; dimensions: 66" L x 23.75" W x 38" H; feature: Traditional
-Materials: Solid Wood, Wood Veneer, Others
+Materials: Solid Wood, Wood Veneer.
 Color: Weathered Oak
 Weight: 669.58 lbs</t>
         </is>
@@ -977,36 +974,35 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>KEBBYLL 3 Pc. Set (TV  and  2 PC)</t>
+          <t>KEBBYLL 3 Pc. Set (TV and 2 PC)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-KEBBYLL 3 Pc. Set (TV  and  2 PC) shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Industrial profile gives the space a refined, approachable look. Built from Metal, Paper Veneeer, Engineered Wood and finished in Antique Black  or  Natural Tone tones for a clean, cohesive look.
-Product Dimensions: 60" W x 15 1 or 2"D x 23" H
+KEBBYLL 3 Pc. Set (TV and 2 PC) shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Industrial profile gives the space a refined, approachable look. Built from Metal, Paper Veneeer, Engineered Wood and finished in Antique Black or Natural Tone tones for a clean, cohesive look.
+Product Dimensions: 60"W X 15 1/2"D X 23"H
 Features
 - Industrial
 - Antique Black or Natural Tone
 - Pipe-Inspired Frame
-- Wire Mesh Shelf
-Included items and dimensions:
-- Pier Cabinet: color: Antique Black  or  Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial
-Materials: Metal, Paper Veneeer, Engineered Wood
-Color: Antique Black  or  Natural Tone
+- Wire Mesh Shelf Included items and dimensions:
+- Pier Cabinet: color: Antique Black or Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial
+Materials: Metal, Paper Veneeer, Engineered Wood.
+Color: Antique Black or Natural Tone
 Weight: 227.7 lbs</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Kebbyll 3 Pc. Set (tv  and  2 Pc) | GOODDEGG</t>
+          <t>Kebbyll 3 Pc. Set (tv and 2 Pc) | GOODDEGG</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1096,37 +1092,36 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KEBBYLL 4 Pc. Set (TV  and  2 PC  and  BR)</t>
+          <t>KEBBYLL 4 Pc. Set (TV and 2 PC and BR)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-KEBBYLL 4 Pc. Set (TV  and  2 PC  and  BR) creates a welcoming living area built for everyday comfort. Designed as a living tv console, it pairs easily with surrounding decor. Its Industrial styling keeps the room feeling polished yet comfortable. Crafted with Metal, Paper Veneeer, Engineered Wood, then finished in Antique Black  or  Natural Tone tones to suit a range of interiors.
-Product Dimensions: 60" W x 15 1 or 2"D x 23" H
+KEBBYLL 4 Pc. Set (TV and 2 PC and BR) creates a welcoming living area built for everyday comfort. Designed as a living tv console, it pairs easily with surrounding decor. Its Industrial styling keeps the room feeling polished yet comfortable. Crafted with Metal, Paper Veneeer, Engineered Wood, then finished in Antique Black or Natural Tone tones to suit a range of interiors.
+Product Dimensions: 60"W X 15 1/2"D X 23"H
 Features
 - Industrial
 - Antique Black or Natural Tone
 - Pipe-Inspired Frame
-- Wire Mesh Shelf
-Included items and dimensions:
-- Pier Cabinet: color: Antique Black  or  Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial
-- Bridge: color: Antique Black  or  Natural Tone; dimensions: 68 7 or 8" W x 13 3 or 4"D x 7 1 or 2" H; feature: Industrial
-Materials: Metal, Paper Veneeer, Engineered Wood
-Color: Antique Black  or  Natural Tone
+- Wire Mesh Shelf Included items and dimensions:
+- Pier Cabinet: color: Antique Black or Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial
+- Bridge: color: Antique Black or Natural Tone; dimensions: 68 7 or 8" W x 13 3 or 4"D x 7 1 or 2" H; feature: Industrial
+Materials: Metal, Paper Veneeer, Engineered Wood.
+Color: Antique Black or Natural Tone
 Weight: 276.1 lbs</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Kebbyll 4 Pc. Set (tv  and  2 Pc  and  Br) | GOODDEGG</t>
+          <t>Kebbyll 4 Pc. Set (tv and 2 Pc and Br) | GOODDEGG</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1216,37 +1211,36 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SILVER CREEK TV Console  and  2 Pier Shelves</t>
+          <t>SILVER CREEK TV Console and 2 Pier Shelves</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SILVER CREEK TV Console  and  2 Pier Shelves shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Metal, Tempered Glass, then finished in Brown  or  Silver tones to suit a range of interiors.
-Product Dimensions: 52" W x 20"D x 22 1 or 2" H
+SILVER CREEK TV Console and 2 Pier Shelves shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Metal, Tempered Glass, then finished in Brown or Silver tones to suit a range of interiors.
+Product Dimensions: 52"W X 20"D X 22 1/2"H
 Features
 - Brown or Silver
 - Black Tempered Glass Top
 - Matching Pier Shelf
-- Metal Construction
-Included items and dimensions:
-- CREEK 52" TV Console: color: Brown  or  Silver; dimensions: 52" W x 20"D x 22 1 or 2" H; feature: Contemporary
-- CREEK 2 Pc. Pier Shelves (1 Pair): color: Brown  or  Silver; dimensions: 20 1 or 2" W x 15 1 or 8"D x 65" H; feature: Contemporary
-Materials: Metal, Tempered Glass
-Color: Brown  or  Silver
+- Metal Construction Included items and dimensions:
+- CREEK 52" TV Console: color: Brown or Silver; dimensions: 52" W x 20"D x 22 1 or 2" H; feature: Contemporary
+- CREEK 2 Pc. Pier Shelves (1 Pair): color: Brown or Silver; dimensions: 20 1 or 2" W x 15 1 or 8"D x 65" H; feature: Contemporary
+Materials: Metal, Tempered Glass.
+Color: Brown or Silver
 Weight: 161 lbs</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SILVER CREEK TV Console  &amp;  2 Pier Shelves in Brown  or  Silver | GOOD</t>
+          <t>SILVER CREEK TV Console &amp; 2 Pier Shelves in Brown or Silver | GOOD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,7 +1325,7 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>TV Stand</t>
         </is>
@@ -1345,10 +1339,9 @@
         <is>
           <t>FREE SHIPPING
 HEPBURNE Entertainment Center shapes a comfortable living space with an easy, coordinated presence. This living tv stand is made to fit naturally into the room. A Gold-Capped Legs profile gives the space a refined, approachable look.
-Product Dimensions: 118" W x 18"D x 79" H
+Product Dimensions: 118"W X 18"D X 79"H
 Features
-- Gold-Capped Legs
-Included items and dimensions:
+- Gold-Capped Legs Included items and dimensions:
 - 70" TV Stand: color: Adjustable Shelves; dimensions: 70" W x 18"D x 30" H; feature: LED Light on Pier
 - Right Pier Base With 1 Door (walnut Finish): dimensions: 24" W x 14"D x 49" H
 - Left Pier Base With 1 Door (walnut Finish): dimensions: 24" W x 18"D x 30" H

--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,183 +454,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Walnut</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FM-AC200WN-SET</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FM-AC200WN-SET</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>Accent Set</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Accent Set</t>
+          <t>ARTH 2Pc Accent Set (Chair and Side Table)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>ARTH 2Pc Accent Set (Chair and Side Table)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ARTH 2Pc Accent Set (Chair and Side Table) shapes a comfortable living space with an easy, coordinated presence. This living accent set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.
@@ -644,109 +649,119 @@
 Weight: 39.6 lbs</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ARTH 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ARTH 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
+          <t>ARTH Accent (Chair and Side Table) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ARTH Accent (Chair and Side Table) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARTH</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ARTH</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>2Pc Accent Set (Chair + Side Table)</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM-AC200WN, FM-AC201WN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>FM-AC200WN, FM-AC201WN</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>FM-AC200WN-SET-1.jpg,FM-AC200WN-2.jpg,FM-AC200WN-SET-1.jpg</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="P2" t="n">
         <v>178</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>189</v>
       </c>
+      <c r="R2" t="n">
+        <v>414</v>
+      </c>
       <c r="S2" t="n">
-        <v>414</v>
-      </c>
-      <c r="T2" t="n">
         <v>39.6</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>TABLE: 22.8"L X 29.1"W X 29.1"H, CHAIR: 23.6"L X 23.6"W X 19.7"H</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>TABLE: 22.8"L X 29.1"W X 29.1"H, CHAIR: 23.6"L X 23.6"W X 19.7"H</t>
+          <t>Mid-Century Modern</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Mid-Century Modern</t>
+          <t>Fabric, Solid Wood, Engineered Wood, Wood Veneer</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Fabric, Solid Wood, Engineered Wood, Wood Veneer</t>
+          <t>Mid-Century Modern,Walnut,Fabric, Solid Wood, Engineered Wood, Wood Veneer,Wingback Chair,Boucle Fabric</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Mid-Century Modern,Walnut,Fabric, Solid Wood, Engineered Wood, Wood Veneer,Wingback Chair,Boucle Fabric</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AB2" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Living, Accent Set, ARTH</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Walnut</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FM-AC203WN-SET</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FM-AC203WN-SET</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>Accent Set</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Accent Set</t>
+          <t>SPIEZ 2Pc Accent Set (Chair and Side Table)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>SPIEZ 2Pc Accent Set (Chair and Side Table)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SPIEZ 2Pc Accent Set (Chair and Side Table) ties the living space together with a balanced, inviting feel. As a living accent set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Walnut tones, the Fabric, Solid Wood, Engineered Wood, Wood Veneer build keeps the look polished and practical.
@@ -760,109 +775,119 @@
 Weight: 33 lbs</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SPIEZ 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SPIEZ 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
+          <t>SPIEZ Accent (Chair and Side Table) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SPIEZ Accent (Chair and Side Table) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SPIEZ</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SPIEZ</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>2Pc Accent Set (Chair + Side Table)</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM-AC203WN, FM-AC202WN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>FM-AC203WN, FM-AC202WN</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>FM-AC203WN-1.jpg,FM-AC203WN-SET-1.jpg</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="P3" t="n">
         <v>178</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
         <v>189</v>
       </c>
+      <c r="R3" t="n">
+        <v>354</v>
+      </c>
       <c r="S3" t="n">
-        <v>354</v>
-      </c>
-      <c r="T3" t="n">
         <v>33</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>TABLE: 19.7"L X 19.7"W X 19.7"H, CHAIR: 24.4"L X 26.8"W X 28.3"H</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>TABLE: 19.7"L X 19.7"W X 19.7"H, CHAIR: 24.4"L X 26.8"W X 28.3"H</t>
+          <t>Mid-Century Modern</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Mid-Century Modern</t>
+          <t>Fabric, Solid Wood, Engineered Wood, Wood Veneer</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Fabric, Solid Wood, Engineered Wood, Wood Veneer</t>
+          <t>Mid-Century Modern,Walnut,Fabric, Solid Wood, Engineered Wood, Wood Veneer,Wingback Chair,Boucle Fabric</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Mid-Century Modern,Walnut,Fabric, Solid Wood, Engineered Wood, Wood Veneer,Wingback Chair,Boucle Fabric</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="AB3" t="n">
         <v>5.9</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Living, Accent Set, SPIEZ</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Weathered Oak</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FM5418AK-TV-SET</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FM5418AK-TV-SET</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>TV Console</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TV Console</t>
+          <t>BROMOAK Entertainment Center</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>BROMOAK Entertainment Center</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BROMOAK Entertainment Center ties the living space together with a balanced, inviting feel. As a living tv console, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Weathered Oak tones to suit a range of interiors.
@@ -882,109 +907,119 @@
 Weight: 669.58 lbs</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BROMOAK Entertainment Center in Weathered Oak | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BROMOAK Entertainment Center in Weathered Oak | GOODDEGG</t>
+          <t>The BROMOAK Entertainment Center brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The BROMOAK Entertainment Center brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BROMOAK</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>Entertainment Center</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM5418AK-P-LB, FM5418AK-P-LT, FM5418AK-P-RB, FM5418AK-P-RT, FM5418AK-TV</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>FM5418AK-P-LB, FM5418AK-P-LT, FM5418AK-P-RB, FM5418AK-P-RT, FM5418AK-TV</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>FM5418AK-TV-1-Z.jpg,FM5418AK-TV-2.jpg,FM5418AK-TV-3.jpg,FM5418AK-TV-4.jpg,FM5418AK-TV-5.jpg,FM5418AK-TV-6.jpg</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="P4" t="n">
         <v>2109</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>2199</v>
       </c>
+      <c r="R4" t="n">
+        <v>4947</v>
+      </c>
       <c r="S4" t="n">
-        <v>4947</v>
-      </c>
-      <c r="T4" t="n">
         <v>669.58</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>130"W X 23.5"D X 90"H</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>130"W X 23.5"D X 90"H</t>
+          <t>Traditional</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Traditional</t>
+          <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Solid Wood, Wood Veneer, Others</t>
+          <t>Traditional,Weathered Oak,Solid Wood, Wood Veneer, Others,Dentil Moldings,Reeded Posts,Carved Details</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Traditional,Weathered Oak,Solid Wood, Wood Veneer, Others,Dentil Moldings,Reeded Posts,Carved Details</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="AB4" t="n">
         <v>136.6</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Living, TV Console, BROMOAK</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Antique Black/Natural Tone</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CM5913-TV-3PC</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CM5913-TV-3PC</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>TV Console</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TV Console</t>
+          <t>KEBBYLL 3 Pc. Set (TV and 2 PC)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>KEBBYLL 3 Pc. Set (TV and 2 PC)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KEBBYLL 3 Pc. Set (TV and 2 PC) shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Industrial profile gives the space a refined, approachable look. Built from Metal, Paper Veneeer, Engineered Wood and finished in Antique Black or Natural Tone tones for a clean, cohesive look.
@@ -1000,109 +1035,119 @@
 Weight: 227.7 lbs</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kebbyll 3 Pc. Set (tv and 2 Pc) | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Kebbyll 3 Pc. Set (tv and 2 Pc) | GOODDEGG</t>
+          <t>The KEBBYLL. (TV and ) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The KEBBYLL. (TV and ) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEBBYLL</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>KEBBYLL</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>3 Pc. Set (TV + 2 PC)</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>CM5913-TV-1, CM5913-TV-2, CM5913-PC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>CM5913-TV-1, CM5913-TV-2, CM5913-PC</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
           <t>CM5913-TV-3PC.jpg,CM5913-TV.jpg,CM5913-TV-PC-BR-9.jpg</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="P5" t="n">
         <v>717</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>717</v>
       </c>
+      <c r="R5" t="n">
+        <v>1797</v>
+      </c>
       <c r="S5" t="n">
-        <v>1797</v>
-      </c>
-      <c r="T5" t="n">
         <v>227.7</v>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>60"W X 15 1/2"D X 23"H</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>60"W X 15 1/2"D X 23"H</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Metal, Paper Veneeer, Engineered Wood</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Metal, Paper Veneeer, Engineered Wood</t>
+          <t>Industrial,Antique Black/Natural Tone,Metal, Paper Veneeer, Engineered Wood,Pipe-Inspired Frame,Wire Mesh Shelf</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Industrial,Antique Black/Natural Tone,Metal, Paper Veneeer, Engineered Wood,Pipe-Inspired Frame,Wire Mesh Shelf</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AB5" t="n">
         <v>19.5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Living, TV Console, KEBBYLL</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Antique Black/Natural Tone</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CM5913-TV-4PC</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CM5913-TV-4PC</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>TV Console</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TV Console</t>
+          <t>KEBBYLL 4 Pc. Set (TV and 2 PC and BR)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>KEBBYLL 4 Pc. Set (TV and 2 PC and BR)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KEBBYLL 4 Pc. Set (TV and 2 PC and BR) creates a welcoming living area built for everyday comfort. Designed as a living tv console, it pairs easily with surrounding decor. Its Industrial styling keeps the room feeling polished yet comfortable. Crafted with Metal, Paper Veneeer, Engineered Wood, then finished in Antique Black or Natural Tone tones to suit a range of interiors.
@@ -1119,109 +1164,119 @@
 Weight: 276.1 lbs</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kebbyll 4 Pc. Set (tv and 2 Pc and Br) | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Kebbyll 4 Pc. Set (tv and 2 Pc and Br) | GOODDEGG</t>
+          <t>The KEBBYLL. (TV and and BR) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>The KEBBYLL. (TV and and BR) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEBBYLL</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>KEBBYLL</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
           <t>4 Pc. Set (TV + 2 PC + BR)</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>CM5913-TV-1, CM5913-TV-2, CM5913-PC, CM5913-BR</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CM5913-TV-1, CM5913-TV-2, CM5913-PC, CM5913-BR</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
           <t>CM5913-TV-4PC.jpg,CM5913-TV.jpg,CM5913-TV-PC-BR-9.jpg</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="P6" t="n">
         <v>846</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>846</v>
       </c>
+      <c r="R6" t="n">
+        <v>2097</v>
+      </c>
       <c r="S6" t="n">
-        <v>2097</v>
-      </c>
-      <c r="T6" t="n">
         <v>276.1</v>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>60"W X 15 1/2"D X 23"H</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>60"W X 15 1/2"D X 23"H</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Metal, Paper Veneeer, Engineered Wood</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Metal, Paper Veneeer, Engineered Wood</t>
+          <t>Industrial,Antique Black/Natural Tone,Metal, Paper Veneeer, Engineered Wood,Pipe-Inspired Frame,Wire Mesh Shelf</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Industrial,Antique Black/Natural Tone,Metal, Paper Veneeer, Engineered Wood,Pipe-Inspired Frame,Wire Mesh Shelf</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AB6" t="n">
         <v>23</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Living, TV Console, KEBBYLL</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Brown/Silver</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CM5510-SET</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CM5510-SET</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>TV Console</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TV Console</t>
+          <t>SILVER CREEK TV Console and 2 Pier Shelves</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>SILVER CREEK TV Console and 2 Pier Shelves</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SILVER CREEK TV Console and 2 Pier Shelves shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Metal, Tempered Glass, then finished in Brown or Silver tones to suit a range of interiors.
@@ -1238,104 +1293,114 @@
 Weight: 161 lbs</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SILVER CREEK TV Console &amp; 2 Pier Shelves in Brown Silver | GOOD</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SILVER CREEK TV Console &amp; 2 Pier Shelves in Brown or Silver | GOOD</t>
+          <t>The CREEK TV Console and Pier Shelves brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The CREEK TV Console and Pier Shelves brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVER CREEK</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SILVER CREEK</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>TV Console + 2 Pier Shelves</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>CM5510-TV, CM5510-PC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CM5510-TV, CM5510-PC</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
           <t>CM5510-TV.jpg</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="P7" t="n">
         <v>388</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>388</v>
       </c>
+      <c r="R7" t="n">
+        <v>1014</v>
+      </c>
       <c r="S7" t="n">
-        <v>1014</v>
-      </c>
-      <c r="T7" t="n">
         <v>161</v>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>52"W X 20"D X 22 1/2"H</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52"W X 20"D X 22 1/2"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Metal, Tempered Glass</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Metal, Tempered Glass</t>
+          <t>Contemporary,Brown/Silver,Metal, Tempered Glass,Black Tempered Glass Top,Matching Pier Shelf,Metal Construction</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Contemporary,Brown/Silver,Metal, Tempered Glass,Black Tempered Glass Top,Matching Pier Shelf,Metal Construction</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC7" t="n">
+      <c r="AB7" t="n">
         <v>9</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Living, TV Console, SILVER CREEK</t>
+        </is>
       </c>
     </row>
     <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FM54000WN-TV-SET</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FM54000WN-TV-SET</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>TV Stand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TV Stand</t>
+          <t>HEPBURNE Entertainment Center</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>HEPBURNE Entertainment Center</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 HEPBURNE Entertainment Center shapes a comfortable living space with an easy, coordinated presence. This living tv stand is made to fit naturally into the room. A Gold-Capped Legs profile gives the space a refined, approachable look.
@@ -1348,72 +1413,82 @@
 - Left or right Pier Hutch With LED Lighting (walnut Finish): dimensions: 24" W x 14"D x 49" H</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>HEPBURNE Entertainment Center | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HEPBURNE Entertainment Center | GOODDEGG</t>
+          <t>The HEPBURNE Entertainment Center brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>The HEPBURNE Entertainment Center brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPBURNE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>HEPBURNE</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
           <t>Entertainment Center</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM54000WN-TV-70, FM54000WN-P-RB, FM54000WN-P-LB, FM54000WN-P-H</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>FM54000WN-TV-70, FM54000WN-P-RB, FM54000WN-P-LB, FM54000WN-P-H</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
           <t>FM54000WN-TV-SET-1.jpg,FM54000WN-TV-70-WB-7.jpg,FM54000WN-TV-LED.jpg,FM54000WN-TV-SET-WB-1.jpg,FM54000WN-TV-SET-WB-2.jpg,FM54000WN-TV-SET-WB-3.jpg,FM54000WN-TV-SET-WB-4.jpg,FM54000WN-TV-SET-WB-5.jpg</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="P8" t="n">
         <v>1269</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>1299</v>
       </c>
-      <c r="S8" t="n">
+      <c r="R8" t="n">
         <v>3057</v>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>118"W X 18"D X 79"H</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>118"W X 18"D X 79"H</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>Gold-Capped Legs</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gold-Capped Legs</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Gold-Capped Legs</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AB8" t="n">
         <v>60.8</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Living, TV Stand, HEPBURNE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -637,16 +637,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTH 2Pc Accent Set (Chair and Side Table) shapes a comfortable living space with an easy, coordinated presence. This living accent set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.
-Product Dimensions: TABLE: 22.8"L X 29.1"W X 29.1"H, CHAIR: 23.6"L X 23.6"W X 19.7"H
-Features
-- Wingback Chair Included items and dimensions:
-- Side Table: color: Walnut; dimensions: 23.5" W x 23.5"D x 19.5" H; feature: Mid-Century Modern
-- Accent Chair: color: Walnut or Beige; dimensions: 23" W x 29"D x 29" H; feature: Mid-Century Modern
-Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.
-Color: Walnut
-Weight: 39.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTH 2Pc Accent Set (Chair and Side Table) shapes a comfortable living space with an easy, coordinated presence. This living accent set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: TABLE: 22.8"L X 29.1"W X 29.1"H, CHAIR: 23.6"L X 23.6"W X 19.7"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Wingback Chair Included items and dimensions:&lt;br&gt;
+- Side Table: color: Walnut; dimensions: 23.5" W x 23.5"D x 19.5" H; feature: Mid-Century Modern&lt;br&gt;
+- Accent Chair: color: Walnut or Beige; dimensions: 23" W x 29"D x 29" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -763,16 +763,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SPIEZ 2Pc Accent Set (Chair and Side Table) ties the living space together with a balanced, inviting feel. As a living accent set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Walnut tones, the Fabric, Solid Wood, Engineered Wood, Wood Veneer build keeps the look polished and practical.
-Product Dimensions: TABLE: 19.7"L X 19.7"W X 19.7"H, CHAIR: 24.4"L X 26.8"W X 28.3"H
-Features
-- Wingback Chair Included items and dimensions:
-- Side Table: color: Walnut; dimensions: 19.5" W x 19.5"D x 19.5" H; feature: Mid-Century Modern
-- Accent Chair: color: Walnut or Beige; dimensions: 24.5" W x 27"D x 28" H; feature: Mid-Century Modern
-Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.
-Color: Walnut
-Weight: 33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SPIEZ 2Pc Accent Set (Chair and Side Table) ties the living space together with a balanced, inviting feel. As a living accent set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Walnut tones, the Fabric, Solid Wood, Engineered Wood, Wood Veneer build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: TABLE: 19.7"L X 19.7"W X 19.7"H, CHAIR: 24.4"L X 26.8"W X 28.3"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Wingback Chair Included items and dimensions:&lt;br&gt;
+- Side Table: color: Walnut; dimensions: 19.5" W x 19.5"D x 19.5" H; feature: Mid-Century Modern&lt;br&gt;
+- Accent Chair: color: Walnut or Beige; dimensions: 24.5" W x 27"D x 28" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -889,22 +889,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BROMOAK Entertainment Center ties the living space together with a balanced, inviting feel. As a living tv console, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Weathered Oak tones to suit a range of interiors.
-Product Dimensions: 130"W X 23.5"D X 90"H
-Features
-- Traditional
-- Dentil Moldings
-- Reeded Posts
-- Carved Details Included items and dimensions:
-- Left Facing Unit Base: color: Weathered Oak; dimensions: 27.75" L x 21.75" W x 34" H; feature: Traditional
-- Left Facing Unit Top: color: Weathered Oak; dimensions: 32" L x 23" W x 56" H; feature: Traditional
-- Right Facing Unit Base: color: Weathered Oak; dimensions: 27.75" L x 21.75" W x 34" H; feature: Traditional
-- Right Facing Unit Top: color: Weathered Oak; dimensions: 32" L x 23" W x 56" H; feature: Traditional
-- Console Base: color: Weathered Oak; dimensions: 66" L x 23.75" W x 38" H; feature: Traditional
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 669.58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BROMOAK Entertainment Center ties the living space together with a balanced, inviting feel. As a living tv console, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Weathered Oak tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 130"W X 23.5"D X 90"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dentil Moldings&lt;br&gt;
+- Reeded Posts&lt;br&gt;
+- Carved Details Included items and dimensions:&lt;br&gt;
+- Left Facing Unit Base: color: Weathered Oak; dimensions: 27.75" L x 21.75" W x 34" H; feature: Traditional&lt;br&gt;
+- Left Facing Unit Top: color: Weathered Oak; dimensions: 32" L x 23" W x 56" H; feature: Traditional&lt;br&gt;
+- Right Facing Unit Base: color: Weathered Oak; dimensions: 27.75" L x 21.75" W x 34" H; feature: Traditional&lt;br&gt;
+- Right Facing Unit Top: color: Weathered Oak; dimensions: 32" L x 23" W x 56" H; feature: Traditional&lt;br&gt;
+- Console Base: color: Weathered Oak; dimensions: 66" L x 23.75" W x 38" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 669.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1021,18 +1021,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KEBBYLL 3 Pc. Set (TV and 2 PC) shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Industrial profile gives the space a refined, approachable look. Built from Metal, Paper Veneeer, Engineered Wood and finished in Antique Black or Natural Tone tones for a clean, cohesive look.
-Product Dimensions: 60"W X 15 1/2"D X 23"H
-Features
-- Industrial
-- Antique Black or Natural Tone
-- Pipe-Inspired Frame
-- Wire Mesh Shelf Included items and dimensions:
-- Pier Cabinet: color: Antique Black or Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial
-Materials: Metal, Paper Veneeer, Engineered Wood.
-Color: Antique Black or Natural Tone
-Weight: 227.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KEBBYLL 3 Pc. Set (TV and 2 PC) shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Industrial profile gives the space a refined, approachable look. Built from Metal, Paper Veneeer, Engineered Wood and finished in Antique Black or Natural Tone tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 60"W X 15 1/2"D X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Industrial&lt;br&gt;
+- Antique Black or Natural Tone&lt;br&gt;
+- Pipe-Inspired Frame&lt;br&gt;
+- Wire Mesh Shelf Included items and dimensions:&lt;br&gt;
+- Pier Cabinet: color: Antique Black or Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Paper Veneeer, Engineered Wood.&lt;br&gt;
+Color: Antique Black or Natural Tone&lt;br&gt;
+Weight: 227.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1149,19 +1149,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KEBBYLL 4 Pc. Set (TV and 2 PC and BR) creates a welcoming living area built for everyday comfort. Designed as a living tv console, it pairs easily with surrounding decor. Its Industrial styling keeps the room feeling polished yet comfortable. Crafted with Metal, Paper Veneeer, Engineered Wood, then finished in Antique Black or Natural Tone tones to suit a range of interiors.
-Product Dimensions: 60"W X 15 1/2"D X 23"H
-Features
-- Industrial
-- Antique Black or Natural Tone
-- Pipe-Inspired Frame
-- Wire Mesh Shelf Included items and dimensions:
-- Pier Cabinet: color: Antique Black or Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial
-- Bridge: color: Antique Black or Natural Tone; dimensions: 68 7 or 8" W x 13 3 or 4"D x 7 1 or 2" H; feature: Industrial
-Materials: Metal, Paper Veneeer, Engineered Wood.
-Color: Antique Black or Natural Tone
-Weight: 276.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KEBBYLL 4 Pc. Set (TV and 2 PC and BR) creates a welcoming living area built for everyday comfort. Designed as a living tv console, it pairs easily with surrounding decor. Its Industrial styling keeps the room feeling polished yet comfortable. Crafted with Metal, Paper Veneeer, Engineered Wood, then finished in Antique Black or Natural Tone tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 60"W X 15 1/2"D X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Industrial&lt;br&gt;
+- Antique Black or Natural Tone&lt;br&gt;
+- Pipe-Inspired Frame&lt;br&gt;
+- Wire Mesh Shelf Included items and dimensions:&lt;br&gt;
+- Pier Cabinet: color: Antique Black or Natural Tone; dimensions: 21 1 or 4" W x 14"D x 62 1 or 2" H; feature: Industrial&lt;br&gt;
+- Bridge: color: Antique Black or Natural Tone; dimensions: 68 7 or 8" W x 13 3 or 4"D x 7 1 or 2" H; feature: Industrial&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Paper Veneeer, Engineered Wood.&lt;br&gt;
+Color: Antique Black or Natural Tone&lt;br&gt;
+Weight: 276.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1278,19 +1278,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SILVER CREEK TV Console and 2 Pier Shelves shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Metal, Tempered Glass, then finished in Brown or Silver tones to suit a range of interiors.
-Product Dimensions: 52"W X 20"D X 22 1/2"H
-Features
-- Brown or Silver
-- Black Tempered Glass Top
-- Matching Pier Shelf
-- Metal Construction Included items and dimensions:
-- CREEK 52" TV Console: color: Brown or Silver; dimensions: 52" W x 20"D x 22 1 or 2" H; feature: Contemporary
-- CREEK 2 Pc. Pier Shelves (1 Pair): color: Brown or Silver; dimensions: 20 1 or 2" W x 15 1 or 8"D x 65" H; feature: Contemporary
-Materials: Metal, Tempered Glass.
-Color: Brown or Silver
-Weight: 161 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SILVER CREEK TV Console and 2 Pier Shelves shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Metal, Tempered Glass, then finished in Brown or Silver tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 52"W X 20"D X 22 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Brown or Silver&lt;br&gt;
+- Black Tempered Glass Top&lt;br&gt;
+- Matching Pier Shelf&lt;br&gt;
+- Metal Construction Included items and dimensions:&lt;br&gt;
+- CREEK 52" TV Console: color: Brown or Silver; dimensions: 52" W x 20"D x 22 1 or 2" H; feature: Contemporary&lt;br&gt;
+- CREEK 2 Pc. Pier Shelves (1 Pair): color: Brown or Silver; dimensions: 20 1 or 2" W x 15 1 or 8"D x 65" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Brown or Silver&lt;br&gt;
+Weight: 161 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1402,15 +1402,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HEPBURNE Entertainment Center shapes a comfortable living space with an easy, coordinated presence. This living tv stand is made to fit naturally into the room. A Gold-Capped Legs profile gives the space a refined, approachable look.
-Product Dimensions: 118"W X 18"D X 79"H
-Features
-- Gold-Capped Legs Included items and dimensions:
-- 70" TV Stand: color: Adjustable Shelves; dimensions: 70" W x 18"D x 30" H; feature: LED Light on Pier
-- Right Pier Base With 1 Door (walnut Finish): dimensions: 24" W x 14"D x 49" H
-- Left Pier Base With 1 Door (walnut Finish): dimensions: 24" W x 18"D x 30" H
-- Left or right Pier Hutch With LED Lighting (walnut Finish): dimensions: 24" W x 14"D x 49" H</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HEPBURNE Entertainment Center shapes a comfortable living space with an easy, coordinated presence. This living tv stand is made to fit naturally into the room. A Gold-Capped Legs profile gives the space a refined, approachable look.&lt;br&gt;
+Product Dimensions: 118"W X 18"D X 79"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gold-Capped Legs Included items and dimensions:&lt;br&gt;
+- 70" TV Stand: color: Adjustable Shelves; dimensions: 70" W x 18"D x 30" H; feature: LED Light on Pier&lt;br&gt;
+- Right Pier Base With 1 Door (walnut Finish): dimensions: 24" W x 14"D x 49" H&lt;br&gt;
+- Left Pier Base With 1 Door (walnut Finish): dimensions: 24" W x 18"D x 30" H&lt;br&gt;
+- Left or right Pier Hutch With LED Lighting (walnut Finish): dimensions: 24" W x 14"D x 49" H&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -731,7 +746,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Living, Accent Set, ARTH</t>
+          <t>Living, Accent Set, ARTH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -857,7 +887,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Living, Accent Set, SPIEZ</t>
+          <t>Living, Accent Set, SPIEZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -989,7 +1034,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Living, TV Console, BROMOAK</t>
+          <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1177,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Living, TV Console, KEBBYLL</t>
+          <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1321,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Living, TV Console, KEBBYLL</t>
+          <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1465,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Living, TV Console, SILVER CREEK</t>
+          <t>Living, TV Console, SILVER CREEK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1592,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Living, TV Stand, HEPBURNE</t>
+          <t>Living, TV Stand, HEPBURNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>

--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">

--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,12 +666,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ARTH 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
+          <t>ARTH 2Pc Accent Set (Chair and Side Table) | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ARTH Accent (Chair and Side Table) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARTH 2Pc Accent Set (Chair and Side Table) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SPIEZ 2Pc Accent Set (Chair and Side Table) in Walnut | GOODDEGG</t>
+          <t>SPIEZ 2Pc Accent Set (Chair and Side Table) | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SPIEZ Accent (Chair and Side Table) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SPIEZ 2Pc Accent Set (Chair and Side Table) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BROMOAK Entertainment Center in Weathered Oak | GOODDEGG</t>
+          <t>BROMOAK Entertainment Center | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The BROMOAK Entertainment Center brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK Entertainment Center TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kebbyll 3 Pc. Set (tv and 2 Pc) | GOODDEGG</t>
+          <t>KEBBYLL 3 Pc. Set (TV and 2 PC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The KEBBYLL. (TV and ) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEBBYLL 3 Pc. Set (TV and 2 PC) TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kebbyll 4 Pc. Set (tv and 2 Pc and Br) | GOODDEGG</t>
+          <t>KEBBYLL 4 Pc. Set (TV and 2 PC and BR) | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The KEBBYLL. (TV and and BR) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TV Console KEBBYLL 4 Pc. Set (TV and 2 PC and supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SILVER CREEK TV Console &amp; 2 Pier Shelves in Brown Silver | GOOD</t>
+          <t>SILVER CREEK TV Console and 2 Pier Shelves | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The CREEK TV Console and Pier Shelves brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVER CREEK TV Console and 2 Pier Shelves supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The HEPBURNE Entertainment Center brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPBURNE Entertainment Center TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/FOA SETS/Living-Set.xlsx
+++ b/FOA SETS/Living-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,171 +454,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
@@ -627,30 +642,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>arth-2pc-accent-set-chair-and-side-table</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Walnut</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>FM-AC200WN-SET</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Accent Set</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ARTH 2Pc Accent Set (Chair and Side Table)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ARTH 2Pc Accent Set (Chair and Side Table) shapes a comfortable living space with an easy, coordinated presence. This living accent set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.&lt;br&gt;
@@ -664,102 +684,108 @@
 Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ARTH 2Pc Accent Set (Chair and Side Table) | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>ARTH 2Pc Accent Set (Chair and Side Table) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>ARTH</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2Pc Accent Set (Chair + Side Table)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>FM-AC200WN, FM-AC201WN</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>FM-AC200WN-SET-1.jpg,FM-AC200WN-2.jpg,FM-AC200WN-SET-1.jpg</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>FM-AC200WN-SET-1.jpg,FM-AC200WN-2.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>178</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>189</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>414</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>39.6</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>TABLE: 22.8"L X 29.1"W X 29.1"H, CHAIR: 23.6"L X 23.6"W X 19.7"H</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Mid-Century Modern</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Fabric, Solid Wood, Engineered Wood, Wood Veneer</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Mid-Century Modern,Walnut,Fabric, Solid Wood, Engineered Wood, Wood Veneer,Wingback Chair,Boucle Fabric</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>8.5</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Living, Accent Set, ARTH, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
@@ -768,30 +794,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>spiez-2pc-accent-set-chair-and-side-table</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Walnut</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FM-AC203WN-SET</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Accent Set</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SPIEZ 2Pc Accent Set (Chair and Side Table)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SPIEZ 2Pc Accent Set (Chair and Side Table) ties the living space together with a balanced, inviting feel. As a living accent set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Walnut tones, the Fabric, Solid Wood, Engineered Wood, Wood Veneer build keeps the look polished and practical.&lt;br&gt;
@@ -805,102 +836,108 @@
 Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SPIEZ 2Pc Accent Set (Chair and Side Table) | GOODDEGG</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>SPIEZ 2Pc Accent Set (Chair and Side Table) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>SPIEZ</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2Pc Accent Set (Chair + Side Table)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>FM-AC203WN, FM-AC202WN</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>FM-AC203WN-1.jpg,FM-AC203WN-SET-1.jpg</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>FM-AC203WN-1.jpg,FM-AC203WN-SET-1.jpg</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>178</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="T3" s="1" t="n">
         <v>189</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>354</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>33</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>TABLE: 19.7"L X 19.7"W X 19.7"H, CHAIR: 24.4"L X 26.8"W X 28.3"H</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Mid-Century Modern</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Fabric, Solid Wood, Engineered Wood, Wood Veneer</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Mid-Century Modern,Walnut,Fabric, Solid Wood, Engineered Wood, Wood Veneer,Wingback Chair,Boucle Fabric</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Living, Accent Set, SPIEZ, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
@@ -909,30 +946,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>bromoak-entertainment-center</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Weathered Oak</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>FM5418AK-TV-SET</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>BROMOAK Entertainment Center</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BROMOAK Entertainment Center ties the living space together with a balanced, inviting feel. As a living tv console, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Weathered Oak tones to suit a range of interiors.&lt;br&gt;
@@ -952,102 +994,108 @@
 Weight: 669.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>BROMOAK Entertainment Center | GOODDEGG</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BROMOAK Entertainment Center TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>BROMOAK</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Entertainment Center</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>FM5418AK-P-LB, FM5418AK-P-LT, FM5418AK-P-RB, FM5418AK-P-RT, FM5418AK-TV</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>FM5418AK-TV-1-Z.jpg,FM5418AK-TV-2.jpg,FM5418AK-TV-3.jpg,FM5418AK-TV-4.jpg,FM5418AK-TV-5.jpg,FM5418AK-TV-6.jpg</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>FM5418AK-TV-1-Z.jpg,FM5418AK-TV-2.jpg,FM5418AK-TV-3.jpg,FM5418AK-TV-4.jpg,FM5418AK-TV-5.jpg,FM5418AK-TV-6.jpg</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>2109</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>2199</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>4947</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>669.58</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>130"W X 23.5"D X 90"H</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Traditional</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Traditional,Weathered Oak,Solid Wood, Wood Veneer, Others,Dentil Moldings,Reeded Posts,Carved Details</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>136.6</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
@@ -1056,30 +1104,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>kebbyll-3-pc-set-tv-and-2-pc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Antique Black/Natural Tone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CM5913-TV-3PC</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>KEBBYLL 3 Pc. Set (TV and 2 PC)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KEBBYLL 3 Pc. Set (TV and 2 PC) shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Industrial profile gives the space a refined, approachable look. Built from Metal, Paper Veneeer, Engineered Wood and finished in Antique Black or Natural Tone tones for a clean, cohesive look.&lt;br&gt;
@@ -1095,102 +1148,108 @@
 Weight: 227.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>KEBBYLL 3 Pc. Set (TV and 2 PC) | GOODDEGG</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>KEBBYLL 3 Pc. Set (TV and 2 PC) TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>KEBBYLL</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>3 Pc. Set (TV + 2 PC)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>CM5913-TV-1, CM5913-TV-2, CM5913-PC</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>CM5913-TV-3PC.jpg,CM5913-TV.jpg,CM5913-TV-PC-BR-9.jpg</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CM5913-TV-3PC.jpg,CM5913-TV.jpg,CM5913-TV-PC-BR-9.jpg</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
         <v>717</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="T5" s="1" t="n">
         <v>717</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>1797</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>227.7</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>60"W X 15 1/2"D X 23"H</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Industrial</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Metal, Paper Veneeer, Engineered Wood</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Industrial,Antique Black/Natural Tone,Metal, Paper Veneeer, Engineered Wood,Pipe-Inspired Frame,Wire Mesh Shelf</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>19.5</v>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
@@ -1199,30 +1258,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>kebbyll-4-pc-set-tv-and-2-pc-and-br</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Antique Black/Natural Tone</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CM5913-TV-4PC</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>KEBBYLL 4 Pc. Set (TV and 2 PC and BR)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KEBBYLL 4 Pc. Set (TV and 2 PC and BR) creates a welcoming living area built for everyday comfort. Designed as a living tv console, it pairs easily with surrounding decor. Its Industrial styling keeps the room feeling polished yet comfortable. Crafted with Metal, Paper Veneeer, Engineered Wood, then finished in Antique Black or Natural Tone tones to suit a range of interiors.&lt;br&gt;
@@ -1239,102 +1303,108 @@
 Weight: 276.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>KEBBYLL 4 Pc. Set (TV and 2 PC and BR) | GOODDEGG</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>TV Console KEBBYLL 4 Pc. Set (TV and 2 PC and supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>KEBBYLL</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>4 Pc. Set (TV + 2 PC + BR)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>CM5913-TV-1, CM5913-TV-2, CM5913-PC, CM5913-BR</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>CM5913-TV-4PC.jpg,CM5913-TV.jpg,CM5913-TV-PC-BR-9.jpg</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CM5913-TV-4PC.jpg,CM5913-TV.jpg,CM5913-TV-PC-BR-9.jpg</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>846</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="T6" s="1" t="n">
         <v>846</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>2097</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>276.1</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>60"W X 15 1/2"D X 23"H</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Industrial</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Metal, Paper Veneeer, Engineered Wood</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Industrial,Antique Black/Natural Tone,Metal, Paper Veneeer, Engineered Wood,Pipe-Inspired Frame,Wire Mesh Shelf</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>23</v>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
@@ -1343,30 +1413,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>silver-creek-tv-console-and-2-pier-shelves</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Brown/Silver</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CM5510-SET</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>TV Console</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>SILVER CREEK TV Console and 2 Pier Shelves</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SILVER CREEK TV Console and 2 Pier Shelves shapes a comfortable living space with an easy, coordinated presence. This living tv console is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Metal, Tempered Glass, then finished in Brown or Silver tones to suit a range of interiors.&lt;br&gt;
@@ -1383,129 +1458,140 @@
 Weight: 161 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>SILVER CREEK TV Console and 2 Pier Shelves | GOODDEGG</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SILVER CREEK TV Console and 2 Pier Shelves supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>SILVER CREEK</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TV Console + 2 Pier Shelves</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>CM5510-TV, CM5510-PC</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>CM5510-TV.jpg</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>CM5510-TV.jpg</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>388</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>388</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>1014</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>161</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>52"W X 20"D X 22 1/2"H</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Metal, Tempered Glass</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Contemporary,Brown/Silver,Metal, Tempered Glass,Black Tempered Glass Top,Matching Pier Shelf,Metal Construction</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>9</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Living, TV Console, SILVER CREEK, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hepburne-entertainment-center</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>FM54000WN-TV-SET</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Living</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>TV Stand</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>HEPBURNE Entertainment Center</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 HEPBURNE Entertainment Center shapes a comfortable living space with an easy, coordinated presence. This living tv stand is made to fit naturally into the room. A Gold-Capped Legs profile gives the space a refined, approachable look.&lt;br&gt;
@@ -1518,94 +1604,100 @@
 - Left or right Pier Hutch With LED Lighting (walnut Finish): dimensions: 24" W x 14"D x 49" H&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>HEPBURNE Entertainment Center | GOODDEGG</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>HEPBURNE Entertainment Center TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>HEPBURNE</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Entertainment Center</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>FM54000WN-TV-70, FM54000WN-P-RB, FM54000WN-P-LB, FM54000WN-P-H</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>FM54000WN-TV-SET-1.jpg,FM54000WN-TV-70-WB-7.jpg,FM54000WN-TV-LED.jpg,FM54000WN-TV-SET-WB-1.jpg,FM54000WN-TV-SET-WB-2.jpg,FM54000WN-TV-SET-WB-3.jpg,FM54000WN-TV-SET-WB-4.jpg,FM54000WN-TV-SET-WB-5.jpg</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>FM54000WN-TV-SET-1.jpg,FM54000WN-TV-70-WB-7.jpg,FM54000WN-TV-LED.jpg,FM54000WN-TV-SET-WB-1.jpg,FM54000WN-TV-SET-WB-2.jpg,FM54000WN-TV-SET-WB-3.jpg,FM54000WN-TV-SET-WB-4.jpg,FM54000WN-TV-SET-WB-5.jpg</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
         <v>1269</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="T8" s="1" t="n">
         <v>1299</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>3057</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>118"W X 18"D X 79"H</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Gold-Capped Legs</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Gold-Capped Legs</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>60.8</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Living, TV Stand, HEPBURNE, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
